--- a/marketing_surveys/007_donor_demographic_research_survey--marketing_surveys.xlsx
+++ b/marketing_surveys/007_donor_demographic_research_survey--marketing_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -919,12 +919,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>zip_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>Zip 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>address_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>Address 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>motivation</t>
+          <t>motivation_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>motivation</t>
+          <t>Motivation 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1542,7 +1542,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>motivation_choices</t>
+          <t>motivation_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1559,7 +1559,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>motivation_choices</t>
+          <t>motivation_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1576,7 +1576,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>motivation_choices</t>
+          <t>motivation_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
